--- a/KHD_資産管理シート_統合版_v1.xlsx
+++ b/KHD_資産管理シート_統合版_v1.xlsx
@@ -529,8 +529,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ガクエンヒルズ北千住901
-(個人保有)</t>
+          <t>北千住戸建
+(足立区千住元町・個人保有)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -583,9 +583,9 @@
           <t>岩手県盛岡市高松二丁目</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>東京都足立区千住5丁目1番3号</t>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>東京都足立区千住元町（番地は謄本23-70／購入時資料11-12の表記差異あり・要確認）</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>区分マンション 2LDK 58.64㎡</t>
+          <t>戸建（1971年築）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>東京メトロ日比谷線「北千住」徒歩10分</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -664,9 +664,9 @@
           <t>要確認</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>平成20年7月（築約17年）</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>1971年（築約54年）</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -687,9 +687,9 @@
       <c r="D11" s="6" t="n">
         <v>2026.5</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>要確認（2025年頃）</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2021年10月（売買契約2021-10-15）</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -710,10 +710,8 @@
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>要確認（非公開・入札）</t>
-        </is>
+      <c r="E12" s="5" t="n">
+        <v>8000000</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>43000000</v>
@@ -735,9 +733,9 @@
           <t>アーバンキューブ側に一括計上中</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2025年に売却検討で入札プロセスあり。現況の保有継続可否は要確認</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>購入価格800万円（うち消費税39,624円）。想定売却価格1,100万円（シミュレーション上）</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -785,10 +783,8 @@
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
+      <c r="E15" s="5" t="n">
+        <v>6000000</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>43000000</v>
@@ -812,7 +808,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2.900%（固定/変動要確認）</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>要確認（2025年時点で別途700万円ベースの返済予定表あり・借換え等の可能性、要確認）</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -918,9 +914,9 @@
           <t>賃貸（長期保有・将来解体検討）</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>要確認（現況：空き）</t>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>賃貸中（定期借家契約2024年1月締結）</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -947,7 +943,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>保有継続 or 売却の方針確認要</t>
+          <t>賃貸中・保有継続（2025年6月時点で固定資産税納付・謄本取得の記録あり）</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
